--- a/Testing Documentation/Validation Plan.xlsx
+++ b/Testing Documentation/Validation Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Testing Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{B649F633-ED46-423E-8B0B-0BF8E4D54EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3BB1C44-24DD-43E0-AB19-D48DB92697D0}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{B649F633-ED46-423E-8B0B-0BF8E4D54EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F671A9A7-ED76-4AB4-B6DA-F61C04635EDE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{755BE624-C457-4E03-B52A-8C1E2975D6CD}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>Test Description</t>
   </si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>Test shall ensure that operator can succesfully startup system in both from off, standby, and fault conditions</t>
-  </si>
-  <si>
-    <t>In Progress</t>
   </si>
   <si>
     <t>1. Validates  Internal Memory Storage of PLC
@@ -100,11 +97,6 @@
     <t>1. Validates Calibration Of Instruments for Final Use By Operator
 2. Provides Creedance to additional  Testing to Validate Process Control Accuracy.
 3. Permits for readable and accessible data collection for operator usage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Compare measurements of RTDs, Flow Meter, Conductivity Sensor, &amp; Valve Postion with calibrated instruments and ensure accuracy
-2. Measurements of RTDs, Flow Meters, Conductivity Sensor, and Valve Positions shall be precice, such that trends are consistent and non noisy 
-</t>
   </si>
   <si>
     <t>1. Disconnect the following sensors one at a time and observe alarms: RTD 1, RTD2, RTD3, Valve Feedback, Conductivity Analog, Flow Sensor, Voltage Sensor, and current sensor
@@ -228,12 +220,95 @@
 10. Shutdown system during pump switching.
 11. Engage pump cylcing, allow pump to almost reach limit, then rebalance pumps</t>
   </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Compare measurements of RTDs, Flow Meter, Conductivity Sensor, &amp; Valve Postion with calibrate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>d instruments and ensure accuracy
+2. Measurements of RTDs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Flow Meters, Conductivity Sensor, and Valve Positions shall be precice, such that trends are consistent and non</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> noisy 
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">• RTD, Analog Conductivity, Flow Completed for Accuaracy
+• Will Add 1xt LP Filters for Precsion
+•Finalize proof 
+</t>
+  </si>
+  <si>
+    <t>• Effectivley completed by usage of operation.
+• Run test on complete skid, and finialize proof.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•Not to be started until final completion of skid
+</t>
+  </si>
+  <si>
+    <t>• Not to be started until final completion of skid</t>
+  </si>
+  <si>
+    <t>• Effectively complete, but will need to run final test on built skid
+• Finalize proof</t>
+  </si>
+  <si>
+    <t>• Logic and interlocks mostly tested and successful
+• Hypothetical tests indicate promissing results
+• Final test on completed skid to validate power
+• Finalize proof</t>
+  </si>
+  <si>
+    <t>• Fault conditions to be final tests - allowing for continued testing and operation of skid during construction.</t>
+  </si>
+  <si>
+    <t>• Data collection possible and bit-wise proof
+• Test on full skid and unreadable SD for full run.
+• Finalize proof</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,6 +320,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -270,7 +351,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -296,7 +377,7 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -304,8 +385,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -641,17 +725,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ACC6211-2444-45CC-8588-C9BB2EE241DD}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="41.6640625" style="6" customWidth="1"/>
     <col min="4" max="4" width="34" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -664,124 +749,147 @@
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>8</v>
+      <c r="E4" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="144" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+    <row r="5" spans="1:6" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="D8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="12"/>
-    </row>
-    <row r="4" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="B9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>34</v>
+      <c r="E9" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/Testing Documentation/Validation Plan.xlsx
+++ b/Testing Documentation/Validation Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Testing Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{B649F633-ED46-423E-8B0B-0BF8E4D54EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F671A9A7-ED76-4AB4-B6DA-F61C04635EDE}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="8_{B649F633-ED46-423E-8B0B-0BF8E4D54EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55A3C751-EC34-4966-ACA5-B681E8AD8CA8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{755BE624-C457-4E03-B52A-8C1E2975D6CD}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
   <si>
     <t>Test Description</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Outcomes</t>
   </si>
   <si>
-    <t>Complete</t>
-  </si>
-  <si>
     <t>Test Name</t>
   </si>
   <si>
@@ -62,26 +59,12 @@
     <t>Test shall ensure that measurements taken from instruments are accurate and precise within a reasonable range</t>
   </si>
   <si>
-    <t>Test shall ensure that operator can succesfully startup system in both from off, standby, and fault conditions</t>
-  </si>
-  <si>
-    <t>1. Validates  Internal Memory Storage of PLC
-2. Validates Software Sequence Operation &amp; Safety Interlock for Faults
-3. Validates Adequate Power Distribution &amp; Protection  to PLC and instrumentation</t>
-  </si>
-  <si>
-    <t>During operation, the operator will remove data lines and/or denergize various instruments and observe the resulting behavior of the PLC</t>
-  </si>
-  <si>
-    <t>During operation, the operator will change the setpoint of the temperature. The result of these changes shall be observed both in the physical instruments and PLC\</t>
+    <t>In Progress</t>
   </si>
   <si>
     <t>Pump Turnover Testing</t>
   </si>
   <si>
-    <t>During operation, the system will attempt to automaically conduct switches to pumps, for cycling, and for hydraulic failures. Additionally, the operator may also wish to switch pumps. Conditions which allow, and prevent switches and potential faults, shall be considered here.</t>
-  </si>
-  <si>
     <t>Fault Conditions</t>
   </si>
   <si>
@@ -91,37 +74,58 @@
     <t xml:space="preserve">Sensor Failure </t>
   </si>
   <si>
-    <t>The system shall encounter various fault conditions during operatrion of the skid. This test will attempt to explore all of these, and subsequent correctoin, observing results.</t>
-  </si>
-  <si>
-    <t>1. Validates Calibration Of Instruments for Final Use By Operator
-2. Provides Creedance to additional  Testing to Validate Process Control Accuracy.
+    <t>Manual Control</t>
+  </si>
+  <si>
+    <t>System Startup &amp; Shutdown</t>
+  </si>
+  <si>
+    <t>Data Collection</t>
+  </si>
+  <si>
+    <t>1. Validates communication, observation, accuracy and precision of all instruments.
+2. Validates software interaction with all instruments, and ability to record data
+3. Validates power distribution on fully active system.</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>• Not to be started until final completion of skid</t>
+  </si>
+  <si>
+    <t>• Effectively complete, but will need to run final test on built skid
+• Finalize proof</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Not started</t>
+  </si>
+  <si>
+    <t>1. Compare measurements of RTDs, Flow Meter, Conductivity Sensor, &amp; Valve Position with calibrated instruments and ensure accuracy
+2. Measurements of RTDs, Flow Meters, Conductivity Sensor, and Valve Positions shall be precise, such that trends are consistent and non-noisy</t>
+  </si>
+  <si>
+    <t>1. Validates Calibration of Instruments for Final Use by Operator
+2. Provides Creedance to additional Testing to Validate Process Control Accuracy
 3. Permits for readable and accessible data collection for operator usage</t>
   </si>
   <si>
-    <t>1. Disconnect the following sensors one at a time and observe alarms: RTD 1, RTD2, RTD3, Valve Feedback, Conductivity Analog, Flow Sensor, Voltage Sensor, and current sensor
-2. Disconnect 2 RTDs and observe results
-3. Disconnected the Water Low Low Line and observe Results
-4. Disconnect Digital Conductivity Sensors and Raise Conductivity to alarm and faults points
-5. Denergize 3-Way Valve During Operation - observe results.
-6. Denergize conductivity PLC and observe results</t>
-  </si>
-  <si>
-    <t>1. Validates instrumentation connection to PLC. 
-2. Validates adequate power distribution, and adaptability to changing loads.
-3. Validates software fault and alarm interlocks, and detectablility of bad signals</t>
-  </si>
-  <si>
-    <t>Manual Control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The operator may be allowed to play with the valve and fans manually. </t>
-  </si>
-  <si>
-    <t>System Startup &amp; Shutdown</t>
-  </si>
-  <si>
-    <t>1. Ensure system is denenergized
+    <t xml:space="preserve">• RTD, Analog Conductivity, Flow Completed for Accuracy
+• Will Implement1st LP Filters for Precision
+• Finalize proof 
+</t>
+  </si>
+  <si>
+    <t>Tests shall ensure that operators can successfully startup system in both from off, standby, and fault states</t>
+  </si>
+  <si>
+    <t>1. Ensure system is deenergized
 2. From a deenergized state, bring the system to running state
 3. From a standby state, bring the system to a running state
 4. From a fault state, bring the system to a running state.
@@ -129,178 +133,143 @@
 6. Ensure physical shutdown switch works</t>
   </si>
   <si>
-    <t>1. Toggle manual fan control  and force fan operation during stadnby, diagnostics, initilization, running, and fault phases. 
-2. Play with valve position manually during all system states and phases.</t>
-  </si>
-  <si>
-    <t>Data Collection</t>
-  </si>
-  <si>
-    <t>The operator may desire to collect data. This test ensures that this is possible, and that a full SD card does not interfer with operations</t>
-  </si>
-  <si>
-    <t>1. Collect data of all instruments during operation and store on SD card.
-2. Create condition for unreadable SD card, and ensure system operation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.Validates Regulation Ability of Temperature Controller in Software
-2. Validates Exception Catching of Software system
-3. Validates Interlocking behavior of software system.
-3. Validates accuracy, precision and observability of RTDs
-4. Validates accuracy, precsion observablity and controlabilty of 3-way-valve instrument
-5. Validates steady state distribution of power to PLC and instruments
-6. Validates robustness of power system from constant and variable consunmption of a servo motor
-7. Validates PLC-HMI User Interface
+    <t>1. Validates Internal Memory Storage of PLC
+2. Validates Software Sequence Operation &amp; Safety Interlock for Faults
+3. Validates Adequate Power Distribution &amp; Protection to PLC and instrumentation</t>
+  </si>
+  <si>
+    <t>• Effectively completed by usage of operation
+• Run test on complete skid, and finalize proof</t>
+  </si>
+  <si>
+    <t>During operation, the operator will remove data lines and/or deenergize various instruments and observe the resulting behavior of the PLC</t>
+  </si>
+  <si>
+    <t>1. Disconnect the following sensors one at a time and observe alarms: RTD 1, RTD2, RTD3, Valve Feedback, Conductivity Analog, Flow Sensor, Voltage Sensor, and current sensor
+2. Disconnect 2 RTDs and observe results
+3. Disconnected the Water Low Low Line and observe Results
+4. Disconnect Digital Conductivity Sensors and Raise Conductivity to alarm and faults points
+5. Deenergize 3-Way Valve During Operation - observe results.
+6. Deenergize conductivity PLC and observe resultss</t>
+  </si>
+  <si>
+    <t>1. Validates instrumentation connection to PLC. 
+2. Validates adequate power distribution, and adaptability to changing loads.
+3. Validates software fault and alarm interlocks, and detectability of bad signals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Not to be started until final completion of skid
 </t>
   </si>
   <si>
-    <t>1. Validates control and communication with fan and valve
-2. Validates power distribution and load for changing DC motor loads, and variable servo motor, in various states
-3. Validates operator controllability of fans and valve.
-4. Valididates PLC-HMI Interface</t>
-  </si>
-  <si>
-    <t>1. Validates instrumentation accuracy, precision, and observation
-2. Validates software logic for faults, and fault overrides
-3. Validates power distrubtikon and protection of a constatnly restarting system
-4. Validates power protection against short circuit.
-5. Validates PLC-HMI  Interface</t>
-  </si>
-  <si>
-    <t>1. Validates software interlock and logic for pump switching.
-2. Validates automatic and manual control over pumps.
-3. Validates accuracy, precision, and observaiblity of voltage, current, flow, and pressure instrumentation
-4. Validates power distrubtion and protection across static and changing loads with DC motors.
-5. Validates PLC-HMI  Interface</t>
-  </si>
-  <si>
-    <t>1. Validates communication, observation, accuracy and precision of all instruments.
-2. Validates software interaction with all instruments, and ability to record data
-3. Validates power distribution on fully active system.</t>
+    <t>During operation, the operator will change the setpoint of the temperature. The result of these changes shall be observed both in the physical instruments and PLC</t>
   </si>
   <si>
     <t>1. Increase the setpoint by 1°C, 3°C, and 6°C and observe system response
 2. Decrease the setpoint by 1°C, 3°C, and 6°C and observe system response
 3. Attempt to overflow and underflow setpoints. Observe system response and results
-4. Attempt to change setpoint while system is in diagnostic and initialization phase.
-5. Change setpoint below process variable, manually control valve to cool below setpoint, the disable manual control. Observe results.
-6. Create setpoint change, and then restrict flow to force a system fault.
-7. Change setpoint by -3°C, and whilst chagning change setpoint again by +1°C
-8. Change setpoint and then immediately switch pumps manually.
-9.Change setpoint to lowest possible value from highest possible value. Observe results.
+4. Attempt to change setpoint while system is in diagnostic and initialization phase
+5. Change setpoint below process variable, manually control valve to cool below setpoint, the disable manual control. Observe results
+6. Create setpoint change and then restrict flow to force a system fault
+7. Change setpoint by -3°C, and whilst system adjusts change setpoint again by +1°C
+8. Change setpoint and then immediately switch pumps manually
+9. Change setpoint to lowest possible value from highest possible value. Observe results
 10. Run temperature regulation with 0 fans, 1 fan, and 2 fans engaged</t>
   </si>
   <si>
-    <t>A.  For all faults: after engaging a fault, attempt to restart the system without override, then attempt it with override (but don't fix the fault), and then finally fix the fault, and attempt a restart with an override.
+    <t xml:space="preserve">1. Validates Regulation Ability of Temperature Controller in Software
+2. Validates Exception Catching of Software system
+3. Validates Interlocking behavior of software system
+3. Validates accuracy, precision and observability of RTDs
+4. Validates accuracy, precision observability and controllability of 3-way-valve instrument
+5. Validates steady state distribution of power to PLC and instruments
+6. Validates robustness of power system from constant and variable consumption of a servo motor
+7. Validates PLC-HMI User Interface
+</t>
+  </si>
+  <si>
+    <t>During operation, the system will attempt to automatically conduct switches to pumps, for cycling, and for hydraulic failures. Additionally, the operator may also wish to switch pumps. Conditions which allow and prevent switches and potential faults shall be considered here</t>
+  </si>
+  <si>
+    <t>1. Enable pump cycling and ensure that pumps cycle at "hour" limits.
+2. Engage pump cycling, then engage simplex mode. Ensure pump cycling is automatically disabled. With simplex mode still engaged, attempt to reengage pump cycling.
+3. Manually switch from primary to secondary and back to primary.
+4. Attempt to switch pumps while system is in diagnostic and initialization phase.
+5. Enable simplex mode and attempt to manually switch pumps.
+6.  While simplex mode is disengaged, disconnect a pump from power - observe results. 
+7. Reconnect now de-active pump and disconnect now active pump - observe results.
+8. DO NOT reconnect de-active pump and disconnect active pump. Observe results.
+9. Manually switch a pump. While initializing, create fault condition with level sensors. Observe results.
+10. Shutdown system during pump switching.
+11. Engage pump cycling, allow pump to almost reach limit, then rebalance pumps</t>
+  </si>
+  <si>
+    <t>1. Validates software interlock and logic for pump switching.
+2. Validates automatic and manual control over pumps.
+3. Validates accuracy, precision, and observability of voltage, current, flow, and pressure instrumentation
+4. Validates power distribution and protection across static and changing loads with DC motors.
+5. Validates PLC-HMI Interface</t>
+  </si>
+  <si>
+    <t>• Logic and interlocks mostly tested and successful
+• Hypothetical tests indicate proper system response
+• Final test on completed skid to validate power
+• Finalize proof</t>
+  </si>
+  <si>
+    <t>The system shall encounter various fault conditions during operation of the skid. This test will attempt to explore all of these, and subsequent corrections, observing results</t>
+  </si>
+  <si>
+    <t>A.  For all faults: after engaging a fault, attempt to restart the system without overriding, then attempt it with override (but don't fix the fault), and then finally fix the fault, and attempt a restart with an override.
 B. Engage the following faults, and then correct:
 1. Engage both water low and water low low
-2. Engage only water lowlow
+2. Engage only water lo wlow
 3. Cause conductivity to become high, and then excessive
-4.Lower conductivity threshold in plc program to create anomolous condition
+4.Lower conductivity threshold in plc program to create anomalous condition
 5. Disconnect pump voltage sensor
 6. Engage simplex mode and disconnect pump power. Do this for primary and secondary pumps
-7.  Force valve into manual mode,  and allow temperature to exceed 
+7. Force valve into manual mode, and allow temperature to exceed 
 8. Destabilize P controller for valve and/or PI controller for temperature 
 9. Manually lower flow rate until fault.
 10. Force a short circuit with pump wiring.
 11. Press random buttons
-12. Engage simplex mode, and then drain system of all water. Observe results
+12. Engage simplex mode and then drain system of all water. Observe results
 13. Attempt to start machine with only secondary pump connected.
 14. Attempt to start system with no pumps connected</t>
   </si>
   <si>
-    <t>1. Enable pump cycling, and ensure that pumps cycle at "hour" limits.
-2. Engage pump cycling, then engage simplex mode. Ensure pump cycling is automatically disabled. With simplex mode still engaged, attempt to rengage pump cycling.
-3. Manually switch from primary to secondary and back to primary.
-4. Attempt to switch pumps while system is in diagnostic and initlialization phase.
-5. Enable simplex mode and attempt to manually switch pumps.
-6.  While simplex mode is disengaged, disconnect a pump from power - observe results. 7. Reconnect now deactive pump, and disconnect now active pump - observe results.
-8. DO NOT reconnect deactive pump, and disconnect active pump. Observe results.
-9. Manually switch a pump. While in initializing, create fault condition with level sensors. Observe results.
-10. Shutdown system during pump switching.
-11. Engage pump cylcing, allow pump to almost reach limit, then rebalance pumps</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <r>
-      <t>1. Compare measurements of RTDs, Flow Meter, Conductivity Sensor, &amp; Valve Postion with calibrate</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>d instruments and ensure accuracy
-2. Measurements of RTDs</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Flow Meters, Conductivity Sensor, and Valve Positions shall be precice, such that trends are consistent and non</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> noisy 
-</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">• RTD, Analog Conductivity, Flow Completed for Accuaracy
-• Will Add 1xt LP Filters for Precsion
-•Finalize proof 
-</t>
-  </si>
-  <si>
-    <t>• Effectivley completed by usage of operation.
-• Run test on complete skid, and finialize proof.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•Not to be started until final completion of skid
-</t>
-  </si>
-  <si>
-    <t>• Not to be started until final completion of skid</t>
-  </si>
-  <si>
-    <t>• Effectively complete, but will need to run final test on built skid
-• Finalize proof</t>
-  </si>
-  <si>
-    <t>• Logic and interlocks mostly tested and successful
-• Hypothetical tests indicate promissing results
-• Final test on completed skid to validate power
-• Finalize proof</t>
-  </si>
-  <si>
-    <t>• Fault conditions to be final tests - allowing for continued testing and operation of skid during construction.</t>
+    <t>1. Validates instrumentation accuracy, precision, and observation
+2. Validates software logic for faults, and fault overrides
+3. Validates power distribution and protection of a constantly restarting system
+4. Validates power protection against short circuits
+5. Validates PLC-HMI Interface</t>
+  </si>
+  <si>
+    <t>• Fault conditions to be final tests - allowing for unobstructed continued testing and operation of skid during construction</t>
+  </si>
+  <si>
+    <t>The operator may be allowed to control the valve and fans manually - this test ensures that such a feature is always available</t>
+  </si>
+  <si>
+    <t>1. Toggle manual fan control and force fan operation during standby, diagnostics, initialization, running, and fault phases. 
+2. Play with valve position manually during all system states and phases.</t>
+  </si>
+  <si>
+    <t>1. Validates control and communication with fan and valve
+2. Validates power distribution and load for changing DC motor loads, and variable servo motor, in various states
+3. Validates operator controllability of fans and valve.
+4. Validates PLC-HMI Interface</t>
+  </si>
+  <si>
+    <t>The operator may desire to collect data. This test ensures that this is possible, and that SD card operations does not interfere with operations</t>
+  </si>
+  <si>
+    <t>1. Collect data of all instruments during operation and store on SD card.
+2. Create condition for unreadable SD card, and ensure system operation</t>
   </si>
   <si>
     <t>• Data collection possible and bit-wise proof
-• Test on full skid and unreadable SD for full run.
+• Test on full skid and unreadable SD for full run
 • Finalize proof</t>
   </si>
 </sst>
@@ -308,7 +277,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,12 +289,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -351,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -360,30 +323,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -391,11 +336,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -406,6 +396,21 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8F25778D-7C69-4392-87F8-07D6FE08DC94}" name="Table1" displayName="Table1" ref="A1:F9" totalsRowShown="0" headerRowDxfId="7" dataDxfId="0">
+  <autoFilter ref="A1:F9" xr:uid="{8F25778D-7C69-4392-87F8-07D6FE08DC94}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{C74D6200-52E4-4C68-8FC6-96CCD92C73FB}" name="Test Name" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{073D94DB-AE7C-4281-955E-878875ED77BA}" name="Test Description" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{20D7D759-5AE9-45C8-99C0-722AC298E66A}" name="Test Procedure" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{7636E05A-7137-4040-9F67-8F1EEDD4465F}" name="Outcomes" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{257942A6-991B-4ACE-9517-F749FD04C1C6}" name="Notes" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{A1AE7627-2F9E-434A-810C-73768B43482F}" name="Status" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -730,7 +735,7 @@
   <cols>
     <col min="1" max="1" width="20.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="41.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="41.6640625" style="4" customWidth="1"/>
     <col min="4" max="4" width="34" style="2" customWidth="1"/>
     <col min="5" max="5" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.77734375" customWidth="1"/>
@@ -738,161 +743,189 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="C2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>6</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="144" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="13" t="s">
+      <c r="A3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="364.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="393" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="13" t="s">
+      <c r="B6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="409.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="B7" s="7" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="11" t="s">
+      <c r="C7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>18</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>21</v>
+      <c r="A8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>26</v>
+      <c r="A9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Testing Documentation/Validation Plan.xlsx
+++ b/Testing Documentation/Validation Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Testing Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="8_{B649F633-ED46-423E-8B0B-0BF8E4D54EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55A3C751-EC34-4966-ACA5-B681E8AD8CA8}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="8_{B649F633-ED46-423E-8B0B-0BF8E4D54EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FD5FAC6-468C-4E95-8701-5DE1A421CFA7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{755BE624-C457-4E03-B52A-8C1E2975D6CD}"/>
   </bookViews>
@@ -98,6 +98,11 @@
 • Finalize proof</t>
   </si>
   <si>
+    <t>• Data collection possible and bit-wise proof
+• Test on full skid and unreadable SD for full run.
+• Finalize proof</t>
+  </si>
+  <si>
     <t>Not Started</t>
   </si>
   <si>
@@ -109,11 +114,6 @@
   <si>
     <t>1. Compare measurements of RTDs, Flow Meter, Conductivity Sensor, &amp; Valve Position with calibrated instruments and ensure accuracy
 2. Measurements of RTDs, Flow Meters, Conductivity Sensor, and Valve Positions shall be precise, such that trends are consistent and non-noisy</t>
-  </si>
-  <si>
-    <t>1. Validates Calibration of Instruments for Final Use by Operator
-2. Provides Creedance to additional Testing to Validate Process Control Accuracy
-3. Permits for readable and accessible data collection for operator usage</t>
   </si>
   <si>
     <t xml:space="preserve">• RTD, Analog Conductivity, Flow Completed for Accuracy
@@ -143,14 +143,6 @@
   </si>
   <si>
     <t>During operation, the operator will remove data lines and/or deenergize various instruments and observe the resulting behavior of the PLC</t>
-  </si>
-  <si>
-    <t>1. Disconnect the following sensors one at a time and observe alarms: RTD 1, RTD2, RTD3, Valve Feedback, Conductivity Analog, Flow Sensor, Voltage Sensor, and current sensor
-2. Disconnect 2 RTDs and observe results
-3. Disconnected the Water Low Low Line and observe Results
-4. Disconnect Digital Conductivity Sensors and Raise Conductivity to alarm and faults points
-5. Deenergize 3-Way Valve During Operation - observe results.
-6. Deenergize conductivity PLC and observe resultss</t>
   </si>
   <si>
     <t>1. Validates instrumentation connection to PLC. 
@@ -175,17 +167,6 @@
 8. Change setpoint and then immediately switch pumps manually
 9. Change setpoint to lowest possible value from highest possible value. Observe results
 10. Run temperature regulation with 0 fans, 1 fan, and 2 fans engaged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Validates Regulation Ability of Temperature Controller in Software
-2. Validates Exception Catching of Software system
-3. Validates Interlocking behavior of software system
-3. Validates accuracy, precision and observability of RTDs
-4. Validates accuracy, precision observability and controllability of 3-way-valve instrument
-5. Validates steady state distribution of power to PLC and instruments
-6. Validates robustness of power system from constant and variable consumption of a servo motor
-7. Validates PLC-HMI User Interface
-</t>
   </si>
   <si>
     <t>During operation, the system will attempt to automatically conduct switches to pumps, for cycling, and for hydraulic failures. Additionally, the operator may also wish to switch pumps. Conditions which allow and prevent switches and potential faults shall be considered here</t>
@@ -202,13 +183,6 @@
 9. Manually switch a pump. While initializing, create fault condition with level sensors. Observe results.
 10. Shutdown system during pump switching.
 11. Engage pump cycling, allow pump to almost reach limit, then rebalance pumps</t>
-  </si>
-  <si>
-    <t>1. Validates software interlock and logic for pump switching.
-2. Validates automatic and manual control over pumps.
-3. Validates accuracy, precision, and observability of voltage, current, flow, and pressure instrumentation
-4. Validates power distribution and protection across static and changing loads with DC motors.
-5. Validates PLC-HMI Interface</t>
   </si>
   <si>
     <t>• Logic and interlocks mostly tested and successful
@@ -238,39 +212,65 @@
 14. Attempt to start system with no pumps connected</t>
   </si>
   <si>
+    <t>• Fault conditions to be final tests - allowing for unobstructed continued testing and operation of skid during construction</t>
+  </si>
+  <si>
+    <t>The operator may be allowed to control the valve and fans manually - this test ensures that such a feature is always available</t>
+  </si>
+  <si>
+    <t>1. Toggle manual fan control and force fan operation during standby, diagnostics, initialization, running, and fault phases. 
+2. Play with valve position manually during all system states and phases.</t>
+  </si>
+  <si>
+    <t>The operator may desire to collect data. This test ensures that this is possible, and that SD card operations does not interfere with operations</t>
+  </si>
+  <si>
+    <t>1. Collect data of all instruments during operation and store on SD card.
+2. Create condition for unreadable SD card, and ensure system operation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Validates Regulation Ability of Temperature Controller in Software
+2. Validates Error Prevention of Software system
+3. Validates Interlocking behavior of software system
+3. Validates accuracy, precision and observability of RTDs
+4. Validates accuracy, precision observability and controllability of 3-way-valve instrument
+5. Validates steady state distribution of power to PLC and instruments
+6. Validates robustness of power system from constant and variable consumption of a servo motor
+7. Validates PLC-HMI User Interface
+</t>
+  </si>
+  <si>
+    <t>1. Validates software interlock, logic, and execution for pump switching.
+2. Validates automatic and manual control over pumps.
+3. Validates accuracy, precision, and observability of voltage, current, flow, and pressure instrumentation
+4. Validates power distribution and protection across static and changing loads with DC motors.
+5. Validates PLC-HMI Interface</t>
+  </si>
+  <si>
     <t>1. Validates instrumentation accuracy, precision, and observation
-2. Validates software logic for faults, and fault overrides
+2. Validates software logic, and execution for faults, and fault overrides
 3. Validates power distribution and protection of a constantly restarting system
 4. Validates power protection against short circuits
 5. Validates PLC-HMI Interface</t>
   </si>
   <si>
-    <t>• Fault conditions to be final tests - allowing for unobstructed continued testing and operation of skid during construction</t>
-  </si>
-  <si>
-    <t>The operator may be allowed to control the valve and fans manually - this test ensures that such a feature is always available</t>
-  </si>
-  <si>
-    <t>1. Toggle manual fan control and force fan operation during standby, diagnostics, initialization, running, and fault phases. 
-2. Play with valve position manually during all system states and phases.</t>
+    <t>1. Validates Calibration of Instruments for Final Use by Operator
+2. Provides Creedance to additional Testing to Validate Process Control Accuracy
+3. Permits for readable and accessible data  for operator usage</t>
+  </si>
+  <si>
+    <t>1. Disconnect the following sensors one at a time and observe alarms: RTD 1, RTD2, RTD3, Valve Feedback, Conductivity Analog, Flow Sensor, Voltage Sensor, and current sensor
+2. Disconnect 2 RTDs and observe results
+3. Disconnected the Water Low Low Line and observe Results
+4. Disconnect Digital Conductivity Sensors and Raise Conductivity to alarm and faults points
+5. Deenergize 3-Way Valve During Operation - observe results.
+6. Deenergize conductivity PLC and observe results</t>
   </si>
   <si>
     <t>1. Validates control and communication with fan and valve
 2. Validates power distribution and load for changing DC motor loads, and variable servo motor, in various states
-3. Validates operator controllability of fans and valve.
+3. Validates operator controllability of fans and valve
 4. Validates PLC-HMI Interface</t>
-  </si>
-  <si>
-    <t>The operator may desire to collect data. This test ensures that this is possible, and that SD card operations does not interfere with operations</t>
-  </si>
-  <si>
-    <t>1. Collect data of all instruments during operation and store on SD card.
-2. Create condition for unreadable SD card, and ensure system operation</t>
-  </si>
-  <si>
-    <t>• Data collection possible and bit-wise proof
-• Test on full skid and unreadable SD for full run
-• Finalize proof</t>
   </si>
 </sst>
 </file>
@@ -733,7 +733,7 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.21875" style="2" customWidth="1"/>
     <col min="2" max="2" width="33.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="41.6640625" style="4" customWidth="1"/>
     <col min="4" max="4" width="34" style="2" customWidth="1"/>
@@ -758,7 +758,7 @@
         <v>15</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
@@ -769,10 +769,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>23</v>
@@ -809,16 +809,16 @@
         <v>28</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>31</v>
-      </c>
       <c r="F4" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="364.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -826,19 +826,19 @@
         <v>9</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>33</v>
-      </c>
       <c r="D5" s="7" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="393" customHeight="1" x14ac:dyDescent="0.3">
@@ -846,16 +846,16 @@
         <v>7</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>6</v>
@@ -866,19 +866,19 @@
         <v>8</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
@@ -886,13 +886,13 @@
         <v>11</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>17</v>
@@ -906,16 +906,16 @@
         <v>13</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>6</v>
